--- a/static/migration_templates/07_member_ledger.xlsx
+++ b/static/migration_templates/07_member_ledger.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="member_ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member_ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,15 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>entry_no</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>debit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>posted_by</t>
         </is>
@@ -522,17 +528,18 @@
           <t>Monthly savings</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
@@ -549,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,33 +569,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>PostgreSQL table</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Member subsidiary transactions. txn_type examples: SHARE_SUBSCRIPTION, SAVINGS_DEPOSIT, LOAN_RELEASE. ledger_type: share, savings, loan.</t>
+          <t>member_ledger</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Required columns</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>member_no, txn_date, txn_type, ledger_type</t>
+          <t>Member subsidiary ledger (member_ledger). txn_type examples: SHARE_SUBSCRIPTION, SAVINGS_DEPOSIT, LOAN_RELEASE. ledger_type: share, savings, or loan. Optional entry_no links journal_entry_id.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Required columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>member_no, txn_date, txn_type, ledger_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Paste your data starting row 2 on the main sheet. Do not rename header row.</t>
         </is>

--- a/static/migration_templates/07_member_ledger.xlsx
+++ b/static/migration_templates/07_member_ledger.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member_ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="member_ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
